--- a/patient_registration_form_templates/043_home_health_care_records_release_form--patient_registration_form_templates.xlsx
+++ b/patient_registration_form_templates/043_home_health_care_records_release_form--patient_registration_form_templates.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -676,7 +676,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Signature</t>
+          <t>Signature (2)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -740,12 +740,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>date_signed</t>
+          <t>date_signed_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Date Signed</t>
+          <t>Date Signed 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>signature_info</t>
+          <t>signature_info_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1062,12 +1062,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>signature</t>
+          <t>signature_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Signature</t>
+          <t>Signature (3)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
